--- a/resources/templates/standard/A2200-03.xlsx
+++ b/resources/templates/standard/A2200-03.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="74">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>경영검토 보고서</t>
   </si>
@@ -822,13 +825,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -846,20 +851,20 @@
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
       <c r="V1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD1" s="4"/>
       <c r="AE1" s="4"/>
@@ -932,14 +937,14 @@
     </row>
     <row r="4" ht="15.95" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -947,7 +952,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -959,7 +964,7 @@
       <c r="T4" s="7"/>
       <c r="U4" s="7"/>
       <c r="V4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
@@ -973,7 +978,7 @@
     </row>
     <row r="5" ht="15.95" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -986,7 +991,7 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
@@ -998,7 +1003,7 @@
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
       <c r="V5" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W5" s="9"/>
       <c r="X5" s="9"/>
@@ -1012,7 +1017,7 @@
     </row>
     <row r="6" ht="15.95" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -1047,11 +1052,11 @@
     </row>
     <row r="7" ht="15.95" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -1063,7 +1068,7 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
@@ -1079,7 +1084,7 @@
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
@@ -2507,7 +2512,7 @@
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G50" s="13"/>
       <c r="H50" s="13"/>
@@ -2603,14 +2608,14 @@
     </row>
     <row r="53" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
       <c r="F53" s="15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="15"/>
@@ -3300,7 +3305,7 @@
     </row>
     <row r="74" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -3566,7 +3571,7 @@
     </row>
     <row r="82" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B82" s="22"/>
       <c r="C82" s="22"/>
@@ -3700,14 +3705,14 @@
     </row>
     <row r="86" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A86" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B86" s="22"/>
       <c r="C86" s="22"/>
       <c r="D86" s="22"/>
       <c r="E86" s="22"/>
       <c r="F86" s="23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G86" s="23"/>
       <c r="H86" s="23"/>
@@ -3721,7 +3726,7 @@
       <c r="P86" s="23"/>
       <c r="Q86" s="23"/>
       <c r="R86" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S86" s="24"/>
       <c r="T86" s="24"/>
@@ -3810,7 +3815,7 @@
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G89" s="13"/>
       <c r="H89" s="13"/>
@@ -3906,14 +3911,14 @@
     </row>
     <row r="92" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A92" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
       <c r="E92" s="14"/>
       <c r="F92" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G92" s="15"/>
       <c r="H92" s="15"/>
@@ -4603,7 +4608,7 @@
     </row>
     <row r="113" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
@@ -4869,7 +4874,7 @@
     </row>
     <row r="121" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A121" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B121" s="22"/>
       <c r="C121" s="22"/>
@@ -5003,14 +5008,14 @@
     </row>
     <row r="125" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A125" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B125" s="22"/>
       <c r="C125" s="22"/>
       <c r="D125" s="22"/>
       <c r="E125" s="22"/>
       <c r="F125" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G125" s="23"/>
       <c r="H125" s="23"/>
@@ -5024,7 +5029,7 @@
       <c r="P125" s="23"/>
       <c r="Q125" s="23"/>
       <c r="R125" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S125" s="24"/>
       <c r="T125" s="24"/>
@@ -5113,7 +5118,7 @@
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
       <c r="F128" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G128" s="13"/>
       <c r="H128" s="13"/>
@@ -5209,14 +5214,14 @@
     </row>
     <row r="131" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A131" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
       <c r="D131" s="14"/>
       <c r="E131" s="14"/>
       <c r="F131" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G131" s="15"/>
       <c r="H131" s="15"/>
@@ -5906,7 +5911,7 @@
     </row>
     <row r="152" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A152" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
@@ -6172,7 +6177,7 @@
     </row>
     <row r="160" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A160" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B160" s="22"/>
       <c r="C160" s="22"/>
@@ -6306,14 +6311,14 @@
     </row>
     <row r="164" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A164" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B164" s="22"/>
       <c r="C164" s="22"/>
       <c r="D164" s="22"/>
       <c r="E164" s="22"/>
       <c r="F164" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G164" s="23"/>
       <c r="H164" s="23"/>
@@ -6327,7 +6332,7 @@
       <c r="P164" s="23"/>
       <c r="Q164" s="23"/>
       <c r="R164" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S164" s="24"/>
       <c r="T164" s="24"/>
@@ -6416,7 +6421,7 @@
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
       <c r="F167" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G167" s="13"/>
       <c r="H167" s="13"/>
@@ -6512,14 +6517,14 @@
     </row>
     <row r="170" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A170" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
       <c r="D170" s="14"/>
       <c r="E170" s="14"/>
       <c r="F170" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G170" s="15"/>
       <c r="H170" s="15"/>
@@ -7209,7 +7214,7 @@
     </row>
     <row r="191" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A191" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
@@ -7475,7 +7480,7 @@
     </row>
     <row r="199" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A199" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B199" s="22"/>
       <c r="C199" s="22"/>
@@ -7609,14 +7614,14 @@
     </row>
     <row r="203" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A203" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B203" s="22"/>
       <c r="C203" s="22"/>
       <c r="D203" s="22"/>
       <c r="E203" s="22"/>
       <c r="F203" s="23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G203" s="23"/>
       <c r="H203" s="23"/>
@@ -7630,7 +7635,7 @@
       <c r="P203" s="23"/>
       <c r="Q203" s="23"/>
       <c r="R203" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S203" s="24"/>
       <c r="T203" s="24"/>
@@ -7719,7 +7724,7 @@
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
       <c r="F206" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G206" s="13"/>
       <c r="H206" s="13"/>
@@ -7815,14 +7820,14 @@
     </row>
     <row r="209" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A209" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
       <c r="D209" s="14"/>
       <c r="E209" s="14"/>
       <c r="F209" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G209" s="15"/>
       <c r="H209" s="15"/>
@@ -8512,7 +8517,7 @@
     </row>
     <row r="230" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A230" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
@@ -8778,7 +8783,7 @@
     </row>
     <row r="238" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A238" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B238" s="22"/>
       <c r="C238" s="22"/>
@@ -8912,14 +8917,14 @@
     </row>
     <row r="242" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A242" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B242" s="22"/>
       <c r="C242" s="22"/>
       <c r="D242" s="22"/>
       <c r="E242" s="22"/>
       <c r="F242" s="23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G242" s="23"/>
       <c r="H242" s="23"/>
@@ -8933,7 +8938,7 @@
       <c r="P242" s="23"/>
       <c r="Q242" s="23"/>
       <c r="R242" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S242" s="24"/>
       <c r="T242" s="24"/>
@@ -9022,7 +9027,7 @@
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
       <c r="F245" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G245" s="13"/>
       <c r="H245" s="13"/>
@@ -9118,14 +9123,14 @@
     </row>
     <row r="248" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A248" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
       <c r="D248" s="14"/>
       <c r="E248" s="14"/>
       <c r="F248" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G248" s="15"/>
       <c r="H248" s="15"/>
@@ -9815,7 +9820,7 @@
     </row>
     <row r="269" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A269" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
@@ -10081,7 +10086,7 @@
     </row>
     <row r="277" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A277" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B277" s="22"/>
       <c r="C277" s="22"/>
@@ -10215,14 +10220,14 @@
     </row>
     <row r="281" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A281" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B281" s="22"/>
       <c r="C281" s="22"/>
       <c r="D281" s="22"/>
       <c r="E281" s="22"/>
       <c r="F281" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G281" s="23"/>
       <c r="H281" s="23"/>
@@ -10236,7 +10241,7 @@
       <c r="P281" s="23"/>
       <c r="Q281" s="23"/>
       <c r="R281" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S281" s="24"/>
       <c r="T281" s="24"/>
@@ -10325,7 +10330,7 @@
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
       <c r="F284" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G284" s="13"/>
       <c r="H284" s="13"/>
@@ -10421,14 +10426,14 @@
     </row>
     <row r="287" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A287" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
       <c r="D287" s="14"/>
       <c r="E287" s="14"/>
       <c r="F287" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G287" s="15"/>
       <c r="H287" s="15"/>
@@ -11118,7 +11123,7 @@
     </row>
     <row r="308" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A308" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
@@ -11384,7 +11389,7 @@
     </row>
     <row r="316" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A316" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B316" s="22"/>
       <c r="C316" s="22"/>
@@ -11518,14 +11523,14 @@
     </row>
     <row r="320" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A320" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B320" s="22"/>
       <c r="C320" s="22"/>
       <c r="D320" s="22"/>
       <c r="E320" s="22"/>
       <c r="F320" s="23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G320" s="23"/>
       <c r="H320" s="23"/>
@@ -11539,7 +11544,7 @@
       <c r="P320" s="23"/>
       <c r="Q320" s="23"/>
       <c r="R320" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S320" s="24"/>
       <c r="T320" s="24"/>
@@ -11628,7 +11633,7 @@
       <c r="D323" s="1"/>
       <c r="E323" s="1"/>
       <c r="F323" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G323" s="13"/>
       <c r="H323" s="13"/>
@@ -11724,14 +11729,14 @@
     </row>
     <row r="326" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A326" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
       <c r="D326" s="14"/>
       <c r="E326" s="14"/>
       <c r="F326" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G326" s="15"/>
       <c r="H326" s="15"/>
@@ -12421,7 +12426,7 @@
     </row>
     <row r="347" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A347" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
@@ -12687,7 +12692,7 @@
     </row>
     <row r="355" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A355" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B355" s="22"/>
       <c r="C355" s="22"/>
@@ -12821,14 +12826,14 @@
     </row>
     <row r="359" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A359" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B359" s="22"/>
       <c r="C359" s="22"/>
       <c r="D359" s="22"/>
       <c r="E359" s="22"/>
       <c r="F359" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G359" s="23"/>
       <c r="H359" s="23"/>
@@ -12842,7 +12847,7 @@
       <c r="P359" s="23"/>
       <c r="Q359" s="23"/>
       <c r="R359" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S359" s="24"/>
       <c r="T359" s="24"/>
@@ -12931,7 +12936,7 @@
       <c r="D362" s="1"/>
       <c r="E362" s="1"/>
       <c r="F362" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G362" s="13"/>
       <c r="H362" s="13"/>
@@ -13027,14 +13032,14 @@
     </row>
     <row r="365" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A365" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
       <c r="D365" s="14"/>
       <c r="E365" s="14"/>
       <c r="F365" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G365" s="15"/>
       <c r="H365" s="15"/>
@@ -13069,7 +13074,7 @@
       <c r="D366" s="14"/>
       <c r="E366" s="14"/>
       <c r="F366" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G366" s="16"/>
       <c r="H366" s="16"/>
@@ -13726,7 +13731,7 @@
     </row>
     <row r="386" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A386" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
@@ -13992,7 +13997,7 @@
     </row>
     <row r="394" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A394" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B394" s="22"/>
       <c r="C394" s="22"/>
@@ -14126,14 +14131,14 @@
     </row>
     <row r="398" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A398" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B398" s="22"/>
       <c r="C398" s="22"/>
       <c r="D398" s="22"/>
       <c r="E398" s="22"/>
       <c r="F398" s="23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G398" s="23"/>
       <c r="H398" s="23"/>
@@ -14147,7 +14152,7 @@
       <c r="P398" s="23"/>
       <c r="Q398" s="23"/>
       <c r="R398" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S398" s="24"/>
       <c r="T398" s="24"/>
@@ -14236,7 +14241,7 @@
       <c r="D401" s="1"/>
       <c r="E401" s="1"/>
       <c r="F401" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G401" s="13"/>
       <c r="H401" s="13"/>
@@ -14332,14 +14337,14 @@
     </row>
     <row r="404" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A404" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B404" s="14"/>
       <c r="C404" s="14"/>
       <c r="D404" s="14"/>
       <c r="E404" s="14"/>
       <c r="F404" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G404" s="15"/>
       <c r="H404" s="15"/>
@@ -15029,7 +15034,7 @@
     </row>
     <row r="425" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A425" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B425" s="14"/>
       <c r="C425" s="14"/>
@@ -15295,7 +15300,7 @@
     </row>
     <row r="433" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A433" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B433" s="22"/>
       <c r="C433" s="22"/>
@@ -15429,14 +15434,14 @@
     </row>
     <row r="437" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A437" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B437" s="22"/>
       <c r="C437" s="22"/>
       <c r="D437" s="22"/>
       <c r="E437" s="22"/>
       <c r="F437" s="23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G437" s="23"/>
       <c r="H437" s="23"/>
@@ -15450,7 +15455,7 @@
       <c r="P437" s="23"/>
       <c r="Q437" s="23"/>
       <c r="R437" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S437" s="24"/>
       <c r="T437" s="24"/>
@@ -15539,7 +15544,7 @@
       <c r="D440" s="1"/>
       <c r="E440" s="1"/>
       <c r="F440" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G440" s="13"/>
       <c r="H440" s="13"/>
@@ -15635,14 +15640,14 @@
     </row>
     <row r="443" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A443" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B443" s="14"/>
       <c r="C443" s="14"/>
       <c r="D443" s="14"/>
       <c r="E443" s="14"/>
       <c r="F443" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G443" s="15"/>
       <c r="H443" s="15"/>
@@ -16332,7 +16337,7 @@
     </row>
     <row r="464" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A464" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B464" s="14"/>
       <c r="C464" s="14"/>
@@ -16598,7 +16603,7 @@
     </row>
     <row r="472" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A472" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B472" s="22"/>
       <c r="C472" s="22"/>
@@ -16732,14 +16737,14 @@
     </row>
     <row r="476" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A476" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B476" s="22"/>
       <c r="C476" s="22"/>
       <c r="D476" s="22"/>
       <c r="E476" s="22"/>
       <c r="F476" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G476" s="23"/>
       <c r="H476" s="23"/>
@@ -16753,7 +16758,7 @@
       <c r="P476" s="23"/>
       <c r="Q476" s="23"/>
       <c r="R476" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S476" s="24"/>
       <c r="T476" s="24"/>
@@ -16842,7 +16847,7 @@
       <c r="D479" s="1"/>
       <c r="E479" s="1"/>
       <c r="F479" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G479" s="13"/>
       <c r="H479" s="13"/>
@@ -16938,14 +16943,14 @@
     </row>
     <row r="482" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A482" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B482" s="14"/>
       <c r="C482" s="14"/>
       <c r="D482" s="14"/>
       <c r="E482" s="14"/>
       <c r="F482" s="15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G482" s="15"/>
       <c r="H482" s="15"/>
@@ -17635,7 +17640,7 @@
     </row>
     <row r="503" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A503" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B503" s="14"/>
       <c r="C503" s="14"/>
@@ -17901,7 +17906,7 @@
     </row>
     <row r="511" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A511" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B511" s="22"/>
       <c r="C511" s="22"/>
@@ -18035,14 +18040,14 @@
     </row>
     <row r="515" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A515" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B515" s="22"/>
       <c r="C515" s="22"/>
       <c r="D515" s="22"/>
       <c r="E515" s="22"/>
       <c r="F515" s="23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G515" s="23"/>
       <c r="H515" s="23"/>
@@ -18056,7 +18061,7 @@
       <c r="P515" s="23"/>
       <c r="Q515" s="23"/>
       <c r="R515" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S515" s="24"/>
       <c r="T515" s="24"/>
@@ -18145,7 +18150,7 @@
       <c r="D518" s="1"/>
       <c r="E518" s="1"/>
       <c r="F518" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G518" s="13"/>
       <c r="H518" s="13"/>
@@ -18241,14 +18246,14 @@
     </row>
     <row r="521" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A521" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B521" s="14"/>
       <c r="C521" s="14"/>
       <c r="D521" s="14"/>
       <c r="E521" s="14"/>
       <c r="F521" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G521" s="15"/>
       <c r="H521" s="15"/>
@@ -18938,7 +18943,7 @@
     </row>
     <row r="542" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A542" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B542" s="14"/>
       <c r="C542" s="14"/>
@@ -19204,7 +19209,7 @@
     </row>
     <row r="550" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A550" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B550" s="22"/>
       <c r="C550" s="22"/>
@@ -19338,14 +19343,14 @@
     </row>
     <row r="554" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A554" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B554" s="22"/>
       <c r="C554" s="22"/>
       <c r="D554" s="22"/>
       <c r="E554" s="22"/>
       <c r="F554" s="23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G554" s="23"/>
       <c r="H554" s="23"/>
@@ -19359,7 +19364,7 @@
       <c r="P554" s="23"/>
       <c r="Q554" s="23"/>
       <c r="R554" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S554" s="24"/>
       <c r="T554" s="24"/>
@@ -19448,7 +19453,7 @@
       <c r="D557" s="1"/>
       <c r="E557" s="1"/>
       <c r="F557" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G557" s="13"/>
       <c r="H557" s="13"/>
@@ -19544,14 +19549,14 @@
     </row>
     <row r="560" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A560" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B560" s="14"/>
       <c r="C560" s="14"/>
       <c r="D560" s="14"/>
       <c r="E560" s="14"/>
       <c r="F560" s="15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G560" s="15"/>
       <c r="H560" s="15"/>
@@ -19586,7 +19591,7 @@
       <c r="D561" s="14"/>
       <c r="E561" s="14"/>
       <c r="F561" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G561" s="16"/>
       <c r="H561" s="16"/>
@@ -20243,7 +20248,7 @@
     </row>
     <row r="581" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A581" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B581" s="14"/>
       <c r="C581" s="14"/>
@@ -20509,7 +20514,7 @@
     </row>
     <row r="589" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A589" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B589" s="22"/>
       <c r="C589" s="22"/>
@@ -20643,14 +20648,14 @@
     </row>
     <row r="593" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A593" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B593" s="22"/>
       <c r="C593" s="22"/>
       <c r="D593" s="22"/>
       <c r="E593" s="22"/>
       <c r="F593" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G593" s="23"/>
       <c r="H593" s="23"/>
@@ -20664,7 +20669,7 @@
       <c r="P593" s="23"/>
       <c r="Q593" s="23"/>
       <c r="R593" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S593" s="24"/>
       <c r="T593" s="24"/>
@@ -20753,7 +20758,7 @@
       <c r="D596" s="1"/>
       <c r="E596" s="1"/>
       <c r="F596" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G596" s="13"/>
       <c r="H596" s="13"/>
@@ -20849,14 +20854,14 @@
     </row>
     <row r="599" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A599" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B599" s="14"/>
       <c r="C599" s="14"/>
       <c r="D599" s="14"/>
       <c r="E599" s="14"/>
       <c r="F599" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G599" s="26"/>
       <c r="H599" s="26"/>
@@ -21546,7 +21551,7 @@
     </row>
     <row r="620" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A620" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B620" s="14"/>
       <c r="C620" s="14"/>
@@ -21812,7 +21817,7 @@
     </row>
     <row r="628" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A628" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B628" s="22"/>
       <c r="C628" s="22"/>
@@ -21946,14 +21951,14 @@
     </row>
     <row r="632" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A632" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B632" s="22"/>
       <c r="C632" s="22"/>
       <c r="D632" s="22"/>
       <c r="E632" s="22"/>
       <c r="F632" s="23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G632" s="23"/>
       <c r="H632" s="23"/>
@@ -21967,7 +21972,7 @@
       <c r="P632" s="23"/>
       <c r="Q632" s="23"/>
       <c r="R632" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S632" s="24"/>
       <c r="T632" s="24"/>
@@ -22056,7 +22061,7 @@
       <c r="D635" s="1"/>
       <c r="E635" s="1"/>
       <c r="F635" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G635" s="13"/>
       <c r="H635" s="13"/>
@@ -22152,14 +22157,14 @@
     </row>
     <row r="638" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A638" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B638" s="14"/>
       <c r="C638" s="14"/>
       <c r="D638" s="14"/>
       <c r="E638" s="14"/>
       <c r="F638" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G638" s="15"/>
       <c r="H638" s="15"/>
@@ -22849,7 +22854,7 @@
     </row>
     <row r="659" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A659" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B659" s="14"/>
       <c r="C659" s="14"/>
@@ -23115,7 +23120,7 @@
     </row>
     <row r="667" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A667" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B667" s="22"/>
       <c r="C667" s="22"/>
@@ -23249,14 +23254,14 @@
     </row>
     <row r="671" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A671" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B671" s="22"/>
       <c r="C671" s="22"/>
       <c r="D671" s="22"/>
       <c r="E671" s="22"/>
       <c r="F671" s="23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G671" s="23"/>
       <c r="H671" s="23"/>
@@ -23270,7 +23275,7 @@
       <c r="P671" s="23"/>
       <c r="Q671" s="23"/>
       <c r="R671" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S671" s="24"/>
       <c r="T671" s="24"/>
@@ -23359,7 +23364,7 @@
       <c r="D674" s="1"/>
       <c r="E674" s="1"/>
       <c r="F674" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G674" s="13"/>
       <c r="H674" s="13"/>
@@ -23455,14 +23460,14 @@
     </row>
     <row r="677" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A677" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B677" s="14"/>
       <c r="C677" s="14"/>
       <c r="D677" s="14"/>
       <c r="E677" s="14"/>
       <c r="F677" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G677" s="15"/>
       <c r="H677" s="15"/>
@@ -24152,7 +24157,7 @@
     </row>
     <row r="698" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A698" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B698" s="14"/>
       <c r="C698" s="14"/>
@@ -24418,7 +24423,7 @@
     </row>
     <row r="706" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A706" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B706" s="22"/>
       <c r="C706" s="22"/>
@@ -24552,14 +24557,14 @@
     </row>
     <row r="710" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A710" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B710" s="22"/>
       <c r="C710" s="22"/>
       <c r="D710" s="22"/>
       <c r="E710" s="22"/>
       <c r="F710" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G710" s="23"/>
       <c r="H710" s="23"/>
@@ -24573,7 +24578,7 @@
       <c r="P710" s="23"/>
       <c r="Q710" s="23"/>
       <c r="R710" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S710" s="24"/>
       <c r="T710" s="24"/>
